--- a/su25biomass1.xlsx
+++ b/su25biomass1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9393AA85-3614-43C6-BBB1-066CAAC2FB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12F0812-4732-45A5-AB87-FA8B19843FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1150,9 +1150,6 @@
       <c r="G24">
         <v>10.18</v>
       </c>
-      <c r="H24">
-        <v>420</v>
-      </c>
       <c r="I24">
         <v>4.0599999999999996</v>
       </c>
@@ -1741,9 +1738,6 @@
       <c r="C51" t="s">
         <v>62</v>
       </c>
-      <c r="H51">
-        <v>483</v>
-      </c>
       <c r="I51">
         <v>15.38</v>
       </c>
@@ -1768,6 +1762,9 @@
       </c>
       <c r="C53" t="s">
         <v>64</v>
+      </c>
+      <c r="H53">
+        <v>483</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -1875,14 +1872,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B462E87CCDA0E4AB3F61CEBB8117501" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81f3e62f49d47117f4e3bb445af46677">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="772c1424-85c2-441a-bfd7-8f15f1cf8684" xmlns:ns4="ced3a378-5222-455c-b98f-2fa57f9d5c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="23f0a3dd10f1dccac3bcaa5224c60a24" ns3:_="" ns4:_="">
     <xsd:import namespace="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
@@ -2115,6 +2104,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
   <ds:schemaRefs>
@@ -2124,23 +2121,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D81D5C-26AA-4EEC-93DA-D7C2B9F21AC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2159,6 +2139,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a2761ec8-7198-4440-bea0-e9dd2af28b51}" enabled="1" method="Standard" siteId="{73e15cf5-5dbb-46af-a862-753916269d73}" removed="0"/>

--- a/su25biomass1.xlsx
+++ b/su25biomass1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12F0812-4732-45A5-AB87-FA8B19843FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E0CFB4-899F-4C11-966E-6F52056297EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1872,6 +1872,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B462E87CCDA0E4AB3F61CEBB8117501" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81f3e62f49d47117f4e3bb445af46677">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="772c1424-85c2-441a-bfd7-8f15f1cf8684" xmlns:ns4="ced3a378-5222-455c-b98f-2fa57f9d5c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="23f0a3dd10f1dccac3bcaa5224c60a24" ns3:_="" ns4:_="">
     <xsd:import namespace="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
@@ -2104,14 +2112,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
   <ds:schemaRefs>
@@ -2121,6 +2121,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D81D5C-26AA-4EEC-93DA-D7C2B9F21AC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2139,23 +2156,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{a2761ec8-7198-4440-bea0-e9dd2af28b51}" enabled="1" method="Standard" siteId="{73e15cf5-5dbb-46af-a862-753916269d73}" removed="0"/>

--- a/su25biomass1.xlsx
+++ b/su25biomass1.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Kjuka_MasterThesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E0CFB4-899F-4C11-966E-6F52056297EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44DDEDE6-E095-43D0-BA9E-EB058DE326E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="su25biomass1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="72">
   <si>
     <t>Treatment</t>
   </si>
@@ -44,27 +44,6 @@
     <t>Beetle</t>
   </si>
   <si>
-    <t>Plant ID</t>
-  </si>
-  <si>
-    <t>Total AGB</t>
-  </si>
-  <si>
-    <t>Pod #</t>
-  </si>
-  <si>
-    <t>Seed #</t>
-  </si>
-  <si>
-    <t>Seed Weight</t>
-  </si>
-  <si>
-    <t>Nodule #</t>
-  </si>
-  <si>
-    <t>Total BGB</t>
-  </si>
-  <si>
     <t>Control</t>
   </si>
   <si>
@@ -161,9 +140,6 @@
     <t>C-Ex-5</t>
   </si>
   <si>
-    <t>MP</t>
-  </si>
-  <si>
     <t>MP-Sb-1</t>
   </si>
   <si>
@@ -249,6 +225,33 @@
   </si>
   <si>
     <t>MP-Ex-5</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Total_AGB</t>
+  </si>
+  <si>
+    <t>Pod_num</t>
+  </si>
+  <si>
+    <t>Seed_num</t>
+  </si>
+  <si>
+    <t>Plant_ID</t>
+  </si>
+  <si>
+    <t>Microplastic</t>
+  </si>
+  <si>
+    <t>Seed_weight</t>
+  </si>
+  <si>
+    <t>Nodule_num</t>
+  </si>
+  <si>
+    <t>Total_BGB</t>
   </si>
 </sst>
 </file>
@@ -621,9 +624,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8679B5F4-0F5A-4F61-9192-E53D5500F48B}">
   <dimension ref="A1:I59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,36 +634,36 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
       </c>
       <c r="D2">
         <v>19.3</v>
@@ -681,40 +684,73 @@
         <v>5.79</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>36.369999999999997</v>
+      </c>
+      <c r="E3">
+        <v>53</v>
+      </c>
+      <c r="F3">
+        <v>93</v>
+      </c>
+      <c r="G3">
+        <v>9.07</v>
+      </c>
+      <c r="H3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>42.62</v>
+      </c>
+      <c r="E4">
+        <v>47</v>
+      </c>
+      <c r="F4">
+        <v>88</v>
+      </c>
+      <c r="G4">
+        <v>11.51</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
       </c>
       <c r="I4">
         <v>3.96</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>16.11</v>
@@ -735,15 +771,15 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>32.22</v>
@@ -764,15 +800,15 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
       </c>
       <c r="D7">
         <v>16.72</v>
@@ -786,27 +822,51 @@
       <c r="G7">
         <v>8.18</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>28.72</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>74</v>
+      </c>
+      <c r="G8">
+        <v>7.74</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8">
+        <v>4.87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>3.1</v>
@@ -820,16 +880,22 @@
       <c r="G9">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>28.22</v>
@@ -850,29 +916,44 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>38.36</v>
+      </c>
+      <c r="E11">
+        <v>59</v>
+      </c>
+      <c r="F11">
+        <v>95</v>
+      </c>
+      <c r="G11">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="H11" t="s">
+        <v>63</v>
       </c>
       <c r="I11">
         <v>5.87</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>33.04</v>
@@ -893,43 +974,73 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>34.659999999999997</v>
+      </c>
+      <c r="E13">
+        <v>52</v>
+      </c>
+      <c r="F13">
+        <v>83</v>
+      </c>
+      <c r="G13">
+        <v>8.17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>63</v>
       </c>
       <c r="I13">
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>34.380000000000003</v>
+      </c>
+      <c r="E14">
+        <v>42</v>
+      </c>
+      <c r="F14">
+        <v>89</v>
+      </c>
+      <c r="G14">
+        <v>9.15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>63</v>
       </c>
       <c r="I14">
         <v>5.29</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D15">
         <v>36.51</v>
@@ -943,19 +1054,22 @@
       <c r="G15">
         <v>9.23</v>
       </c>
+      <c r="H15" t="s">
+        <v>63</v>
+      </c>
       <c r="I15">
         <v>5.37</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D16">
         <v>29.64</v>
@@ -976,26 +1090,44 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
         <v>20</v>
       </c>
-      <c r="C17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>35.44</v>
+      </c>
+      <c r="E17">
+        <v>48</v>
+      </c>
+      <c r="F17">
+        <v>97</v>
+      </c>
+      <c r="G17">
+        <v>12.4</v>
+      </c>
+      <c r="H17" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>11.03</v>
@@ -1009,16 +1141,22 @@
       <c r="G18">
         <v>3.87</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D19">
         <v>33.6</v>
@@ -1039,15 +1177,15 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D20">
         <v>28.92</v>
@@ -1068,15 +1206,15 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <v>35.82</v>
@@ -1090,30 +1228,51 @@
       <c r="G21">
         <v>10.46</v>
       </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
       <c r="I21">
-        <v>5.23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10.220000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="D22">
+        <v>36.44</v>
+      </c>
+      <c r="E22">
+        <v>63</v>
+      </c>
+      <c r="F22">
+        <v>101</v>
+      </c>
+      <c r="G22">
+        <v>10.76</v>
+      </c>
+      <c r="H22" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22">
+        <v>7.52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>35.840000000000003</v>
@@ -1127,16 +1286,22 @@
       <c r="G23">
         <v>10.78</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H23" t="s">
+        <v>63</v>
+      </c>
+      <c r="I23">
+        <v>10.029999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D24">
         <v>35.869999999999997</v>
@@ -1150,30 +1315,51 @@
       <c r="G24">
         <v>10.18</v>
       </c>
+      <c r="H24">
+        <v>420</v>
+      </c>
       <c r="I24">
         <v>4.0599999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="D25">
+        <v>38.29</v>
+      </c>
+      <c r="E25">
+        <v>55</v>
+      </c>
+      <c r="F25">
+        <v>79</v>
+      </c>
+      <c r="G25">
+        <v>7.65</v>
+      </c>
+      <c r="H25" t="s">
+        <v>63</v>
+      </c>
+      <c r="I25">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>32.44</v>
@@ -1194,15 +1380,15 @@
         <v>10.54</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D27">
         <v>41.48</v>
@@ -1223,26 +1409,44 @@
         <v>10.86</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="D28">
+        <v>36.020000000000003</v>
+      </c>
+      <c r="E28">
+        <v>54</v>
+      </c>
+      <c r="F28">
+        <v>97</v>
+      </c>
+      <c r="G28">
+        <v>9.56</v>
+      </c>
+      <c r="H28" t="s">
+        <v>63</v>
+      </c>
+      <c r="I28">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D29">
         <v>32.159999999999997</v>
@@ -1256,30 +1460,51 @@
       <c r="G29">
         <v>11.2</v>
       </c>
+      <c r="H29" t="s">
+        <v>63</v>
+      </c>
       <c r="I29">
         <v>7.87</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="D30">
+        <v>33.01</v>
+      </c>
+      <c r="E30">
+        <v>51</v>
+      </c>
+      <c r="F30">
+        <v>89</v>
+      </c>
+      <c r="G30">
+        <v>9.24</v>
+      </c>
+      <c r="H30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I30">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D31">
         <v>46.68</v>
@@ -1300,15 +1525,15 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D32">
         <v>34.9</v>
@@ -1325,27 +1550,48 @@
       <c r="H32">
         <v>618</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <v>5.41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="D33">
+        <v>48.75</v>
+      </c>
+      <c r="E33">
+        <v>63</v>
+      </c>
+      <c r="F33">
+        <v>113</v>
+      </c>
+      <c r="G33">
+        <v>14.09</v>
+      </c>
+      <c r="H33" t="s">
+        <v>63</v>
+      </c>
+      <c r="I33">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D34">
         <v>38.67</v>
@@ -1366,15 +1612,15 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D35">
         <v>37.67</v>
@@ -1391,16 +1637,19 @@
       <c r="H35">
         <v>713</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <v>8.77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D36">
         <v>40.25</v>
@@ -1421,15 +1670,15 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D37">
         <v>42.89</v>
@@ -1450,15 +1699,15 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" t="s">
-        <v>49</v>
       </c>
       <c r="D38">
         <v>48.88</v>
@@ -1479,15 +1728,15 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D39">
         <v>40.15</v>
@@ -1501,16 +1750,22 @@
       <c r="G39">
         <v>14.37</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H39" t="s">
+        <v>63</v>
+      </c>
+      <c r="I39">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D40">
         <v>40.880000000000003</v>
@@ -1524,19 +1779,22 @@
       <c r="G40">
         <v>14.12</v>
       </c>
+      <c r="H40" t="s">
+        <v>63</v>
+      </c>
       <c r="I40">
         <v>4.33</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D41">
         <v>26.22</v>
@@ -1550,19 +1808,22 @@
       <c r="G41">
         <v>14.19</v>
       </c>
+      <c r="H41" t="s">
+        <v>63</v>
+      </c>
       <c r="I41">
         <v>6.04</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D42">
         <v>11.82</v>
@@ -1576,30 +1837,51 @@
       <c r="G42">
         <v>12.3</v>
       </c>
+      <c r="H42" t="s">
+        <v>63</v>
+      </c>
       <c r="I42">
         <v>2.29</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="D43">
+        <v>39.82</v>
+      </c>
+      <c r="E43">
+        <v>59</v>
+      </c>
+      <c r="F43">
+        <v>109</v>
+      </c>
+      <c r="G43">
+        <v>13.61</v>
+      </c>
+      <c r="H43" t="s">
+        <v>63</v>
+      </c>
+      <c r="I43">
+        <v>6.51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D44">
         <v>41.1</v>
@@ -1613,49 +1895,109 @@
       <c r="G44">
         <v>11.25</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H44" t="s">
+        <v>63</v>
+      </c>
+      <c r="I44">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+      <c r="D45">
+        <v>35.25</v>
+      </c>
+      <c r="E45">
+        <v>50</v>
+      </c>
+      <c r="F45">
+        <v>93</v>
+      </c>
+      <c r="G45">
+        <v>14.25</v>
+      </c>
+      <c r="H45" t="s">
+        <v>63</v>
+      </c>
+      <c r="I45">
+        <v>5.83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="D46">
+        <v>13.21</v>
+      </c>
+      <c r="E46">
+        <v>49</v>
+      </c>
+      <c r="F46">
+        <v>95</v>
+      </c>
+      <c r="G46">
+        <v>11.98</v>
+      </c>
+      <c r="H46" t="s">
+        <v>63</v>
+      </c>
+      <c r="I46">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="D47">
+        <v>30.64</v>
+      </c>
+      <c r="E47">
+        <v>44</v>
+      </c>
+      <c r="F47">
+        <v>81</v>
+      </c>
+      <c r="G47">
+        <v>9.24</v>
+      </c>
+      <c r="H47" t="s">
+        <v>63</v>
+      </c>
+      <c r="I47">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D48">
         <v>31.43</v>
@@ -1676,15 +2018,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D49">
         <v>34.54</v>
@@ -1698,16 +2040,22 @@
       <c r="G49">
         <v>6.27</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H49" t="s">
+        <v>63</v>
+      </c>
+      <c r="I49">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D50">
         <v>40.18</v>
@@ -1728,65 +2076,131 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="D51">
+        <v>40.36</v>
+      </c>
+      <c r="E51">
+        <v>59</v>
+      </c>
+      <c r="F51">
+        <v>101</v>
+      </c>
+      <c r="G51">
+        <v>12.59</v>
+      </c>
+      <c r="H51">
+        <v>483</v>
       </c>
       <c r="I51">
-        <v>15.38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="D52">
+        <v>37.99</v>
+      </c>
+      <c r="E52">
+        <v>59</v>
+      </c>
+      <c r="F52">
+        <v>104</v>
+      </c>
+      <c r="G52">
+        <v>11.75</v>
+      </c>
+      <c r="H52" t="s">
+        <v>63</v>
+      </c>
+      <c r="I52">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
-      </c>
-      <c r="H53">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="D53">
+        <v>36.35</v>
+      </c>
+      <c r="E53">
+        <v>52</v>
+      </c>
+      <c r="F53">
+        <v>87</v>
+      </c>
+      <c r="G53">
+        <v>12.23</v>
+      </c>
+      <c r="H53" t="s">
+        <v>63</v>
+      </c>
+      <c r="I53">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="D54">
+        <v>38.29</v>
+      </c>
+      <c r="E54">
+        <v>57</v>
+      </c>
+      <c r="F54">
+        <v>99</v>
+      </c>
+      <c r="G54">
+        <v>11.85</v>
+      </c>
+      <c r="H54" t="s">
+        <v>63</v>
+      </c>
+      <c r="I54">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D55">
         <v>36.31</v>
@@ -1800,38 +2214,80 @@
       <c r="G55">
         <v>11.13</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H55" t="s">
+        <v>63</v>
+      </c>
+      <c r="I55">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="D56">
+        <v>30.78</v>
+      </c>
+      <c r="E56">
+        <v>56</v>
+      </c>
+      <c r="F56">
+        <v>107</v>
+      </c>
+      <c r="G56">
+        <v>12.91</v>
+      </c>
+      <c r="H56" t="s">
+        <v>63</v>
+      </c>
+      <c r="I56">
+        <v>7.44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="D57">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="E57">
+        <v>54</v>
+      </c>
+      <c r="F57">
+        <v>103</v>
+      </c>
+      <c r="G57">
+        <v>11.14</v>
+      </c>
+      <c r="H57" t="s">
+        <v>63</v>
+      </c>
+      <c r="I57">
+        <v>9.8800000000000008</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D58">
         <v>29.85</v>
@@ -1845,16 +2301,40 @@
       <c r="G58">
         <v>11.19</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H58" t="s">
+        <v>63</v>
+      </c>
+      <c r="I58">
+        <v>10.72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="D59">
+        <v>37.14</v>
+      </c>
+      <c r="E59">
+        <v>55</v>
+      </c>
+      <c r="F59">
+        <v>96</v>
+      </c>
+      <c r="G59">
+        <v>11.31</v>
+      </c>
+      <c r="H59" t="s">
+        <v>63</v>
+      </c>
+      <c r="I59">
+        <v>11.85</v>
       </c>
     </row>
   </sheetData>
@@ -1863,23 +2343,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B462E87CCDA0E4AB3F61CEBB8117501" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81f3e62f49d47117f4e3bb445af46677">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="772c1424-85c2-441a-bfd7-8f15f1cf8684" xmlns:ns4="ced3a378-5222-455c-b98f-2fa57f9d5c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="23f0a3dd10f1dccac3bcaa5224c60a24" ns3:_="" ns4:_="">
     <xsd:import namespace="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
@@ -2112,10 +2575,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D81D5C-26AA-4EEC-93DA-D7C2B9F21AC0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2138,20 +2629,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D81D5C-26AA-4EEC-93DA-D7C2B9F21AC0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
-    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/su25biomass1.xlsx
+++ b/su25biomass1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44DDEDE6-E095-43D0-BA9E-EB058DE326E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACAC505-200B-4F83-A9C3-AE54E4A24AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
   </bookViews>
   <sheets>
     <sheet name="su25biomass1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="71">
   <si>
     <t>Treatment</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Control</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>C-Sb-1</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>C-MBB-1</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>C-MBB-2</t>
   </si>
   <si>
@@ -252,6 +246,9 @@
   </si>
   <si>
     <t>Total_BGB</t>
+  </si>
+  <si>
+    <t>No beetle</t>
   </si>
 </sst>
 </file>
@@ -634,25 +631,25 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" t="s">
         <v>69</v>
-      </c>
-      <c r="H1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -660,10 +657,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
       </c>
       <c r="D2">
         <v>19.3</v>
@@ -689,10 +686,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>36.369999999999997</v>
@@ -707,7 +704,7 @@
         <v>9.07</v>
       </c>
       <c r="H3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I3">
         <v>7.89</v>
@@ -718,10 +715,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>42.62</v>
@@ -736,7 +733,7 @@
         <v>11.51</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I4">
         <v>3.96</v>
@@ -747,10 +744,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>16.11</v>
@@ -776,10 +773,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>32.22</v>
@@ -805,10 +802,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>16.72</v>
@@ -823,7 +820,7 @@
         <v>8.18</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I7">
         <v>3.53</v>
@@ -834,10 +831,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>28.72</v>
@@ -852,7 +849,7 @@
         <v>7.74</v>
       </c>
       <c r="H8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I8">
         <v>4.87</v>
@@ -863,10 +860,10 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>3.1</v>
@@ -881,7 +878,7 @@
         <v>1.25</v>
       </c>
       <c r="H9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I9">
         <v>1.43</v>
@@ -892,10 +889,10 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>28.22</v>
@@ -921,10 +918,10 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11">
         <v>38.36</v>
@@ -939,7 +936,7 @@
         <v>8.7200000000000006</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I11">
         <v>5.87</v>
@@ -950,10 +947,10 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>33.04</v>
@@ -979,10 +976,10 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13">
         <v>34.659999999999997</v>
@@ -997,7 +994,7 @@
         <v>8.17</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I13">
         <v>4.6500000000000004</v>
@@ -1008,10 +1005,10 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>34.380000000000003</v>
@@ -1026,7 +1023,7 @@
         <v>9.15</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I14">
         <v>5.29</v>
@@ -1037,10 +1034,10 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>36.51</v>
@@ -1055,7 +1052,7 @@
         <v>9.23</v>
       </c>
       <c r="H15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I15">
         <v>5.37</v>
@@ -1066,10 +1063,10 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D16">
         <v>29.64</v>
@@ -1095,10 +1092,10 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D17">
         <v>35.44</v>
@@ -1113,7 +1110,7 @@
         <v>12.4</v>
       </c>
       <c r="H17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I17">
         <v>2.82</v>
@@ -1124,10 +1121,10 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18">
         <v>11.03</v>
@@ -1142,7 +1139,7 @@
         <v>3.87</v>
       </c>
       <c r="H18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I18">
         <v>3.17</v>
@@ -1153,10 +1150,10 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D19">
         <v>33.6</v>
@@ -1182,10 +1179,10 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20">
         <v>28.92</v>
@@ -1211,10 +1208,10 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>35.82</v>
@@ -1229,7 +1226,7 @@
         <v>10.46</v>
       </c>
       <c r="H21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I21">
         <v>10.220000000000001</v>
@@ -1240,10 +1237,10 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D22">
         <v>36.44</v>
@@ -1258,7 +1255,7 @@
         <v>10.76</v>
       </c>
       <c r="H22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I22">
         <v>7.52</v>
@@ -1269,10 +1266,10 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D23">
         <v>35.840000000000003</v>
@@ -1287,7 +1284,7 @@
         <v>10.78</v>
       </c>
       <c r="H23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I23">
         <v>10.029999999999999</v>
@@ -1298,10 +1295,10 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D24">
         <v>35.869999999999997</v>
@@ -1327,10 +1324,10 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D25">
         <v>38.29</v>
@@ -1345,7 +1342,7 @@
         <v>7.65</v>
       </c>
       <c r="H25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I25">
         <v>7.81</v>
@@ -1356,10 +1353,10 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D26">
         <v>32.44</v>
@@ -1385,10 +1382,10 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>41.48</v>
@@ -1414,10 +1411,10 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D28">
         <v>36.020000000000003</v>
@@ -1432,7 +1429,7 @@
         <v>9.56</v>
       </c>
       <c r="H28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I28">
         <v>4.28</v>
@@ -1443,10 +1440,10 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D29">
         <v>32.159999999999997</v>
@@ -1461,7 +1458,7 @@
         <v>11.2</v>
       </c>
       <c r="H29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I29">
         <v>7.87</v>
@@ -1472,10 +1469,10 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D30">
         <v>33.01</v>
@@ -1490,7 +1487,7 @@
         <v>9.24</v>
       </c>
       <c r="H30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I30">
         <v>4.18</v>
@@ -1498,13 +1495,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D31">
         <v>46.68</v>
@@ -1527,13 +1524,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>34.9</v>
@@ -1556,13 +1553,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D33">
         <v>48.75</v>
@@ -1577,7 +1574,7 @@
         <v>14.09</v>
       </c>
       <c r="H33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I33">
         <v>8.25</v>
@@ -1585,13 +1582,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D34">
         <v>38.67</v>
@@ -1614,13 +1611,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D35">
         <v>37.67</v>
@@ -1643,13 +1640,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D36">
         <v>40.25</v>
@@ -1672,13 +1669,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D37">
         <v>42.89</v>
@@ -1701,13 +1698,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D38">
         <v>48.88</v>
@@ -1730,13 +1727,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D39">
         <v>40.15</v>
@@ -1751,7 +1748,7 @@
         <v>14.37</v>
       </c>
       <c r="H39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I39">
         <v>4.03</v>
@@ -1759,13 +1756,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D40">
         <v>40.880000000000003</v>
@@ -1780,7 +1777,7 @@
         <v>14.12</v>
       </c>
       <c r="H40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I40">
         <v>4.33</v>
@@ -1788,13 +1785,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D41">
         <v>26.22</v>
@@ -1809,7 +1806,7 @@
         <v>14.19</v>
       </c>
       <c r="H41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I41">
         <v>6.04</v>
@@ -1817,13 +1814,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D42">
         <v>11.82</v>
@@ -1838,7 +1835,7 @@
         <v>12.3</v>
       </c>
       <c r="H42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I42">
         <v>2.29</v>
@@ -1846,13 +1843,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D43">
         <v>39.82</v>
@@ -1867,7 +1864,7 @@
         <v>13.61</v>
       </c>
       <c r="H43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I43">
         <v>6.51</v>
@@ -1875,13 +1872,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D44">
         <v>41.1</v>
@@ -1896,7 +1893,7 @@
         <v>11.25</v>
       </c>
       <c r="H44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I44">
         <v>4.18</v>
@@ -1904,13 +1901,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C45" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D45">
         <v>35.25</v>
@@ -1925,7 +1922,7 @@
         <v>14.25</v>
       </c>
       <c r="H45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I45">
         <v>5.83</v>
@@ -1933,13 +1930,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D46">
         <v>13.21</v>
@@ -1954,7 +1951,7 @@
         <v>11.98</v>
       </c>
       <c r="H46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I46">
         <v>2.83</v>
@@ -1962,13 +1959,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D47">
         <v>30.64</v>
@@ -1983,7 +1980,7 @@
         <v>9.24</v>
       </c>
       <c r="H47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I47">
         <v>4.68</v>
@@ -1991,13 +1988,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D48">
         <v>31.43</v>
@@ -2020,13 +2017,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D49">
         <v>34.54</v>
@@ -2041,7 +2038,7 @@
         <v>6.27</v>
       </c>
       <c r="H49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I49">
         <v>5.81</v>
@@ -2049,13 +2046,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D50">
         <v>40.18</v>
@@ -2078,13 +2075,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D51">
         <v>40.36</v>
@@ -2107,13 +2104,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D52">
         <v>37.99</v>
@@ -2128,7 +2125,7 @@
         <v>11.75</v>
       </c>
       <c r="H52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I52">
         <v>5.0599999999999996</v>
@@ -2136,13 +2133,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D53">
         <v>36.35</v>
@@ -2157,7 +2154,7 @@
         <v>12.23</v>
       </c>
       <c r="H53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I53">
         <v>8.56</v>
@@ -2165,13 +2162,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D54">
         <v>38.29</v>
@@ -2186,7 +2183,7 @@
         <v>11.85</v>
       </c>
       <c r="H54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I54">
         <v>5.86</v>
@@ -2194,13 +2191,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D55">
         <v>36.31</v>
@@ -2215,7 +2212,7 @@
         <v>11.13</v>
       </c>
       <c r="H55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I55">
         <v>12.8</v>
@@ -2223,13 +2220,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B56" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C56" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D56">
         <v>30.78</v>
@@ -2244,7 +2241,7 @@
         <v>12.91</v>
       </c>
       <c r="H56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I56">
         <v>7.44</v>
@@ -2252,13 +2249,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D57">
         <v>33.840000000000003</v>
@@ -2273,7 +2270,7 @@
         <v>11.14</v>
       </c>
       <c r="H57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I57">
         <v>9.8800000000000008</v>
@@ -2281,13 +2278,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C58" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D58">
         <v>29.85</v>
@@ -2302,7 +2299,7 @@
         <v>11.19</v>
       </c>
       <c r="H58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I58">
         <v>10.72</v>
@@ -2310,13 +2307,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D59">
         <v>37.14</v>
@@ -2331,7 +2328,7 @@
         <v>11.31</v>
       </c>
       <c r="H59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I59">
         <v>11.85</v>
@@ -2343,6 +2340,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005B462E87CCDA0E4AB3F61CEBB8117501" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="81f3e62f49d47117f4e3bb445af46677">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="772c1424-85c2-441a-bfd7-8f15f1cf8684" xmlns:ns4="ced3a378-5222-455c-b98f-2fa57f9d5c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="23f0a3dd10f1dccac3bcaa5224c60a24" ns3:_="" ns4:_="">
     <xsd:import namespace="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
@@ -2575,14 +2580,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2593,6 +2590,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D81D5C-26AA-4EEC-93DA-D7C2B9F21AC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2611,23 +2625,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
   <ds:schemaRefs>

--- a/su25biomass1.xlsx
+++ b/su25biomass1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oia08\Documents\GitHub\Kjuka_MasterThesis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACAC505-200B-4F83-A9C3-AE54E4A24AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6169E86-4EAD-49A7-8C8A-885F6569B4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{D4E00C66-3BDD-493C-8EBC-085081E15A15}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>Beetle</t>
   </si>
   <si>
-    <t>Control</t>
-  </si>
-  <si>
     <t>C-Sb-1</t>
   </si>
   <si>
@@ -236,9 +233,6 @@
     <t>Plant_ID</t>
   </si>
   <si>
-    <t>Microplastic</t>
-  </si>
-  <si>
     <t>Seed_weight</t>
   </si>
   <si>
@@ -249,6 +243,12 @@
   </si>
   <si>
     <t>No beetle</t>
+  </si>
+  <si>
+    <t>Control,</t>
+  </si>
+  <si>
+    <t>Microplastic,</t>
   </si>
 </sst>
 </file>
@@ -631,36 +631,36 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" t="s">
         <v>65</v>
       </c>
-      <c r="D1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" t="s">
         <v>67</v>
-      </c>
-      <c r="H1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
       </c>
       <c r="D2">
         <v>19.3</v>
@@ -683,13 +683,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>36.369999999999997</v>
@@ -704,7 +704,7 @@
         <v>9.07</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>7.89</v>
@@ -712,13 +712,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>42.62</v>
@@ -733,7 +733,7 @@
         <v>11.51</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4">
         <v>3.96</v>
@@ -741,13 +741,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>16.11</v>
@@ -770,13 +770,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>32.22</v>
@@ -799,13 +799,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>16.72</v>
@@ -820,7 +820,7 @@
         <v>8.18</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I7">
         <v>3.53</v>
@@ -828,13 +828,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>28.72</v>
@@ -849,7 +849,7 @@
         <v>7.74</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8">
         <v>4.87</v>
@@ -857,13 +857,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>3.1</v>
@@ -878,7 +878,7 @@
         <v>1.25</v>
       </c>
       <c r="H9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I9">
         <v>1.43</v>
@@ -886,13 +886,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>28.22</v>
@@ -915,13 +915,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>38.36</v>
@@ -936,7 +936,7 @@
         <v>8.7200000000000006</v>
       </c>
       <c r="H11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I11">
         <v>5.87</v>
@@ -944,13 +944,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12">
         <v>33.04</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13">
         <v>34.659999999999997</v>
@@ -994,7 +994,7 @@
         <v>8.17</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I13">
         <v>4.6500000000000004</v>
@@ -1002,13 +1002,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14">
         <v>34.380000000000003</v>
@@ -1023,7 +1023,7 @@
         <v>9.15</v>
       </c>
       <c r="H14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I14">
         <v>5.29</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>36.51</v>
@@ -1052,7 +1052,7 @@
         <v>9.23</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I15">
         <v>5.37</v>
@@ -1060,13 +1060,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>29.64</v>
@@ -1089,13 +1089,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17">
         <v>35.44</v>
@@ -1110,7 +1110,7 @@
         <v>12.4</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I17">
         <v>2.82</v>
@@ -1118,13 +1118,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18">
         <v>11.03</v>
@@ -1139,7 +1139,7 @@
         <v>3.87</v>
       </c>
       <c r="H18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I18">
         <v>3.17</v>
@@ -1147,13 +1147,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19">
         <v>33.6</v>
@@ -1176,13 +1176,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>28.92</v>
@@ -1205,13 +1205,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21">
         <v>35.82</v>
@@ -1226,7 +1226,7 @@
         <v>10.46</v>
       </c>
       <c r="H21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I21">
         <v>10.220000000000001</v>
@@ -1234,13 +1234,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22">
         <v>36.44</v>
@@ -1255,7 +1255,7 @@
         <v>10.76</v>
       </c>
       <c r="H22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I22">
         <v>7.52</v>
@@ -1263,13 +1263,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23">
         <v>35.840000000000003</v>
@@ -1284,7 +1284,7 @@
         <v>10.78</v>
       </c>
       <c r="H23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I23">
         <v>10.029999999999999</v>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24">
         <v>35.869999999999997</v>
@@ -1321,13 +1321,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25">
         <v>38.29</v>
@@ -1342,7 +1342,7 @@
         <v>7.65</v>
       </c>
       <c r="H25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I25">
         <v>7.81</v>
@@ -1350,13 +1350,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26">
         <v>32.44</v>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27">
         <v>41.48</v>
@@ -1408,13 +1408,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>36.020000000000003</v>
@@ -1429,7 +1429,7 @@
         <v>9.56</v>
       </c>
       <c r="H28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I28">
         <v>4.28</v>
@@ -1437,13 +1437,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29">
         <v>32.159999999999997</v>
@@ -1458,7 +1458,7 @@
         <v>11.2</v>
       </c>
       <c r="H29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I29">
         <v>7.87</v>
@@ -1466,13 +1466,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30">
         <v>33.01</v>
@@ -1487,7 +1487,7 @@
         <v>9.24</v>
       </c>
       <c r="H30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I30">
         <v>4.18</v>
@@ -1495,13 +1495,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31">
         <v>46.68</v>
@@ -1524,13 +1524,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32">
         <v>34.9</v>
@@ -1553,13 +1553,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>48.75</v>
@@ -1574,7 +1574,7 @@
         <v>14.09</v>
       </c>
       <c r="H33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I33">
         <v>8.25</v>
@@ -1582,13 +1582,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>38.67</v>
@@ -1611,13 +1611,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35">
         <v>37.67</v>
@@ -1640,13 +1640,13 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D36">
         <v>40.25</v>
@@ -1669,13 +1669,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37">
         <v>42.89</v>
@@ -1698,13 +1698,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38">
         <v>48.88</v>
@@ -1727,13 +1727,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39">
         <v>40.15</v>
@@ -1748,7 +1748,7 @@
         <v>14.37</v>
       </c>
       <c r="H39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I39">
         <v>4.03</v>
@@ -1756,13 +1756,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40">
         <v>40.880000000000003</v>
@@ -1777,7 +1777,7 @@
         <v>14.12</v>
       </c>
       <c r="H40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I40">
         <v>4.33</v>
@@ -1785,13 +1785,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41">
         <v>26.22</v>
@@ -1806,7 +1806,7 @@
         <v>14.19</v>
       </c>
       <c r="H41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I41">
         <v>6.04</v>
@@ -1814,13 +1814,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42">
         <v>11.82</v>
@@ -1835,7 +1835,7 @@
         <v>12.3</v>
       </c>
       <c r="H42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I42">
         <v>2.29</v>
@@ -1843,13 +1843,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43">
         <v>39.82</v>
@@ -1864,7 +1864,7 @@
         <v>13.61</v>
       </c>
       <c r="H43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I43">
         <v>6.51</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44">
         <v>41.1</v>
@@ -1893,7 +1893,7 @@
         <v>11.25</v>
       </c>
       <c r="H44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I44">
         <v>4.18</v>
@@ -1901,13 +1901,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45">
         <v>35.25</v>
@@ -1922,7 +1922,7 @@
         <v>14.25</v>
       </c>
       <c r="H45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I45">
         <v>5.83</v>
@@ -1930,13 +1930,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46">
         <v>13.21</v>
@@ -1951,7 +1951,7 @@
         <v>11.98</v>
       </c>
       <c r="H46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I46">
         <v>2.83</v>
@@ -1959,13 +1959,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D47">
         <v>30.64</v>
@@ -1980,7 +1980,7 @@
         <v>9.24</v>
       </c>
       <c r="H47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I47">
         <v>4.68</v>
@@ -1988,13 +1988,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D48">
         <v>31.43</v>
@@ -2017,13 +2017,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49">
         <v>34.54</v>
@@ -2038,7 +2038,7 @@
         <v>6.27</v>
       </c>
       <c r="H49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I49">
         <v>5.81</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D50">
         <v>40.18</v>
@@ -2075,13 +2075,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D51">
         <v>40.36</v>
@@ -2104,13 +2104,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B52" t="s">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D52">
         <v>37.99</v>
@@ -2125,7 +2125,7 @@
         <v>11.75</v>
       </c>
       <c r="H52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I52">
         <v>5.0599999999999996</v>
@@ -2133,13 +2133,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53">
         <v>36.35</v>
@@ -2154,7 +2154,7 @@
         <v>12.23</v>
       </c>
       <c r="H53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I53">
         <v>8.56</v>
@@ -2162,13 +2162,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54">
         <v>38.29</v>
@@ -2183,7 +2183,7 @@
         <v>11.85</v>
       </c>
       <c r="H54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I54">
         <v>5.86</v>
@@ -2191,13 +2191,13 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D55">
         <v>36.31</v>
@@ -2212,7 +2212,7 @@
         <v>11.13</v>
       </c>
       <c r="H55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I55">
         <v>12.8</v>
@@ -2220,13 +2220,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D56">
         <v>30.78</v>
@@ -2241,7 +2241,7 @@
         <v>12.91</v>
       </c>
       <c r="H56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I56">
         <v>7.44</v>
@@ -2249,13 +2249,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57">
         <v>33.840000000000003</v>
@@ -2270,7 +2270,7 @@
         <v>11.14</v>
       </c>
       <c r="H57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I57">
         <v>9.8800000000000008</v>
@@ -2278,13 +2278,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D58">
         <v>29.85</v>
@@ -2299,7 +2299,7 @@
         <v>11.19</v>
       </c>
       <c r="H58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I58">
         <v>10.72</v>
@@ -2307,13 +2307,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D59">
         <v>37.14</v>
@@ -2328,7 +2328,7 @@
         <v>11.31</v>
       </c>
       <c r="H59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I59">
         <v>11.85</v>
@@ -2340,11 +2340,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2581,27 +2582,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="772c1424-85c2-441a-bfd7-8f15f1cf8684" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2626,9 +2617,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACACEFE8-BCDE-4A25-B3D9-F098830A1F7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C122F0D-C698-44FF-B804-0E8FDBC87648}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="772c1424-85c2-441a-bfd7-8f15f1cf8684"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced3a378-5222-455c-b98f-2fa57f9d5c74"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
